--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_Fiets.xlsx
@@ -388,13 +388,13 @@
         <v>186262</v>
       </c>
       <c r="C2">
-        <v>270117</v>
+        <v>270573</v>
       </c>
       <c r="D2">
-        <v>316273</v>
+        <v>316484</v>
       </c>
       <c r="E2">
-        <v>341342</v>
+        <v>341401</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -405,13 +405,13 @@
         <v>225117</v>
       </c>
       <c r="C3">
-        <v>323748</v>
+        <v>324395</v>
       </c>
       <c r="D3">
-        <v>373957</v>
+        <v>374134</v>
       </c>
       <c r="E3">
-        <v>405780</v>
+        <v>405830</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -422,13 +422,13 @@
         <v>201010</v>
       </c>
       <c r="C4">
-        <v>299610</v>
+        <v>300222</v>
       </c>
       <c r="D4">
-        <v>354511</v>
+        <v>354738</v>
       </c>
       <c r="E4">
-        <v>387666</v>
+        <v>387709</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -442,7 +442,7 @@
         <v>219786</v>
       </c>
       <c r="D5">
-        <v>246917</v>
+        <v>246918</v>
       </c>
       <c r="E5">
         <v>269806</v>
@@ -479,7 +479,7 @@
         <v>23275</v>
       </c>
       <c r="E7">
-        <v>24997</v>
+        <v>24998</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>705765</v>
       </c>
       <c r="C8">
-        <v>1030473</v>
+        <v>1039861</v>
       </c>
       <c r="D8">
-        <v>1228210</v>
+        <v>1235970</v>
       </c>
       <c r="E8">
-        <v>1334097</v>
+        <v>1335261</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>199454</v>
       </c>
       <c r="C9">
-        <v>280426</v>
+        <v>280616</v>
       </c>
       <c r="D9">
-        <v>318483</v>
+        <v>318521</v>
       </c>
       <c r="E9">
-        <v>344245</v>
+        <v>344253</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>85634</v>
       </c>
       <c r="C10">
-        <v>117365</v>
+        <v>117379</v>
       </c>
       <c r="D10">
-        <v>134776</v>
+        <v>134792</v>
       </c>
       <c r="E10">
-        <v>142996</v>
+        <v>143007</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>15740</v>
+        <v>15746</v>
       </c>
       <c r="C11">
-        <v>20485</v>
+        <v>20492</v>
       </c>
       <c r="D11">
-        <v>23259</v>
+        <v>23263</v>
       </c>
       <c r="E11">
-        <v>26626</v>
+        <v>26629</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>37527</v>
+        <v>37537</v>
       </c>
       <c r="C12">
-        <v>53768</v>
+        <v>53776</v>
       </c>
       <c r="D12">
-        <v>61460</v>
+        <v>61463</v>
       </c>
       <c r="E12">
-        <v>64361</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>48129</v>
       </c>
       <c r="C13">
-        <v>65393</v>
+        <v>65397</v>
       </c>
       <c r="D13">
-        <v>75817</v>
+        <v>75825</v>
       </c>
       <c r="E13">
-        <v>81388</v>
+        <v>81394</v>
       </c>
     </row>
   </sheetData>
